--- a/data/trans_bre/IQ2608_R3-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IQ2608_R3-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,19</t>
+          <t>-3,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-4,55%</t>
+          <t>-4,62%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 4,22</t>
+          <t>-17,75; 5,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 0,29</t>
+          <t>-18,06; 1,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 7,31</t>
+          <t>-11,55; 7,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 15,87</t>
+          <t>-22,48; 16,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 7,59</t>
+          <t>-27,44; 10,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 0,2</t>
+          <t>-19,96; 1,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 9,03</t>
+          <t>-13,11; 9,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 26,21</t>
+          <t>-28,54; 28,12</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,37</t>
+          <t>7,72</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 4,46</t>
+          <t>-18,89; 4,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 8,23</t>
+          <t>-8,09; 7,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 6,95</t>
+          <t>-9,25; 5,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 31,04</t>
+          <t>-14,9; 31,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 6,58</t>
+          <t>-25,78; 6,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 9,94</t>
+          <t>-8,93; 9,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 8,46</t>
+          <t>-10,41; 7,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 68,91</t>
+          <t>-20,64; 70,73</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-21,69</t>
+          <t>-21,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-28,99%</t>
+          <t>-29,15%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 18,38</t>
+          <t>-7,24; 17,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 7,89</t>
+          <t>-10,66; 7,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 6,31</t>
+          <t>-17,85; 7,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-53,12; 8,48</t>
+          <t>-51,49; 9,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 33,8</t>
+          <t>-11,13; 32,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 10,33</t>
+          <t>-11,91; 9,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 8,78</t>
+          <t>-21,48; 11,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,41; 12,55</t>
+          <t>-62,7; 15,26</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,81</t>
+          <t>-4,96</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-4,9%</t>
+          <t>-6,34%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 7,37</t>
+          <t>-8,67; 6,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 4,76</t>
+          <t>-8,61; 5,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 0,49</t>
+          <t>-11,18; 0,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 12,99</t>
+          <t>-23,23; 11,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 12,07</t>
+          <t>-12,24; 10,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 5,99</t>
+          <t>-10,16; 6,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 0,58</t>
+          <t>-12,61; 0,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 19,95</t>
+          <t>-27,32; 16,02</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-8,54</t>
+          <t>-12,38</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-11,91%</t>
+          <t>-17,56%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 7,67</t>
+          <t>-13,08; 7,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 10,09</t>
+          <t>-7,35; 11,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 4,93</t>
+          <t>-9,65; 4,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 13,66</t>
+          <t>-33,31; 7,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 13,46</t>
+          <t>-20,16; 13,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 14,73</t>
+          <t>-9,24; 16,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 5,95</t>
+          <t>-11,04; 5,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 21,86</t>
+          <t>-42,97; 12,89</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-7,73</t>
+          <t>-2,44</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-13,86%</t>
+          <t>-4,74%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,17; -0,04</t>
+          <t>-26,83; 0,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 16,04</t>
+          <t>-5,29; 15,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 11,07</t>
+          <t>-16,68; 10,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,34; 23,16</t>
+          <t>-32,33; 28,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,66; 0,82</t>
+          <t>-38,76; 0,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 21,23</t>
+          <t>-5,94; 20,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 16,49</t>
+          <t>-21,38; 16,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,49; 53,62</t>
+          <t>-51,21; 71,52</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,09</t>
+          <t>-4,63</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-5,86%</t>
+          <t>-6,7%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 0,77</t>
+          <t>-7,9; 1,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 2,86</t>
+          <t>-4,38; 2,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 0,3</t>
+          <t>-6,59; 0,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 4,91</t>
+          <t>-13,63; 4,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 1,26</t>
+          <t>-11,96; 1,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 3,56</t>
+          <t>-5,27; 3,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 0,25</t>
+          <t>-7,79; 0,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 7,64</t>
+          <t>-18,23; 6,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2608_R3-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IQ2608_R3-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-6,63</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-7,9</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,21</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-10,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-9,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-2,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-4,62%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-6.629491216786709</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-7.896438061399536</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.803373684222764</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.206153853472682</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1092678732744276</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.09078292492009014</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.02157254225133592</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.04624708133181257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-17,75; 5,62</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-18,06; 1,6</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-11,55; 7,27</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-22,48; 16,23</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-27,44; 10,35</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-19,96; 1,96</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-13,11; 9,12</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-28,54; 28,12</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-17.74724934863882</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-18.0638835366523</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-11.54704332078004</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-22.48406731495044</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2744006505029074</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1995823794707136</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1310996330268567</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2854244463294942</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.6245522761958</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.596198633164939</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.267432986815672</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>16.23468073370937</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1034692416205596</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.01958035611218961</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.09121431968319414</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.2811756425738581</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-7,29</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,72</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-10,52%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-1,39%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-18,89; 4,49</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-8,09; 7,72</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,25; 5,86</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-14,9; 31,41</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-25,78; 6,76</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-8,93; 9,3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-10,41; 7,04</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-20,64; 70,73</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-7.288248991022462</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.2777388202723663</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.20051675430064</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>7.718796684948104</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1051782542523884</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.003171622630115617</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.01388773168643333</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1254127974141837</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,62</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-21,43</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,97%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-6,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-29,15%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-18.88866365122667</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-8.089143111326475</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-9.252097656266605</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-14.90271823875497</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2578217301976597</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.0892958985722201</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1040513403341738</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2063580026084713</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,24; 17,44</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,66; 7,57</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-17,85; 7,89</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-51,49; 9,33</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-11,13; 32,78</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-11,91; 9,37</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-21,48; 11,2</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-62,7; 15,26</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.492577463302872</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.721500116402741</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.858990421895377</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>31.41354983885068</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.06763465761405038</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.09303196710673632</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.07043765378661546</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.7073078103810474</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-4,96</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-6,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-6,34%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>4.748152113907278</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.671199712239113</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-4.61734406636285</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-21.43154281118962</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.08014534580819187</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.01971221383880118</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.05998785398463721</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2914620734267077</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-8,67; 6,64</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-8,61; 5,12</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-11,18; 0,38</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-23,23; 11,21</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-12,24; 10,55</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-10,16; 6,4</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-12,61; 0,21</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-27,32; 16,02</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.243776635548731</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.66195782831899</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-17.8496249673895</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-51.49116026947132</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.111344381173657</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1191448567931532</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.2147721105715216</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6270307635101253</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>17.44018847916857</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.570066748156407</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.891610313262806</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.325512757666168</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.3277914273536445</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.0936784842519465</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1119917247698215</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.1526154867543894</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,8</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,44</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-12,38</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,6%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-2,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-17,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-13,08; 7,45</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-7,35; 11,08</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-9,65; 4,5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-33,31; 7,73</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-20,16; 13,16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-9,24; 16,38</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-11,04; 5,4</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-42,97; 12,89</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.08992557319991157</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.5112413941332</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-5.395347863584099</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-4.95797621071894</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.001350066563273802</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01831325090848479</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.06213313496343495</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.06339975283615425</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-13,39</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-2,58</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-2,44</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-20,87%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-3,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-4,74%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-8.666941525649005</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-8.614055684204272</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-11.18123466532212</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-23.23076074393841</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.122369699057135</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.101627208296411</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1260822672229042</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2731667749837316</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-26,83; 0,24</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-5,29; 15,04</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-16,68; 10,91</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-32,33; 28,86</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-38,76; 0,39</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-5,94; 20,01</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-21,38; 16,61</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-51,21; 71,52</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.637535437228506</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.12439912525299</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.383810823986022</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>11.21265194949031</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.10546521382842</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.0640491048163938</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.002091860925346934</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.1601817350596895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-3,34</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,13</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-4,63</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-5,24%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-1,13%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-3,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-6,7%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-2.800574699427538</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.900786670824639</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.437131762611811</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-12.38403571749948</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.04603457785192092</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.02600229123371699</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.02858730480460374</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1755547640940825</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-7,9; 1,13</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,38; 2,45</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-6,59; 0,24</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-13,63; 4,06</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-11,96; 1,86</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-5,27; 3,02</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-7,79; 0,3</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-18,23; 6,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-13.08327676953149</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.346680776433108</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-9.650311063737025</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-33.30681972643683</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2015916455311448</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.09239106279801756</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1103540396271129</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4297427266532649</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.454843288129859</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>11.07802996283638</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.502095925449905</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.725604343169828</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.1316147611147176</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1637934520732083</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.0539592628195043</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1289393856220611</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-13.38550525454761</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>5.338312915147913</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-2.581729080454753</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-2.440108651151024</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.2087340224140473</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.06489530281887543</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.03573864162229064</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.04742011680777786</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-26.83436616732588</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-5.28952260833281</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-16.67527497422106</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-32.33203933275718</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.3876117114236679</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.0594130313503748</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.2137905876996566</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.5121389536376506</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.2436105184781572</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>15.03732794809385</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>10.91199582678347</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>28.86430380775151</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.003917900798827247</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.2001153616886331</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.1661010649830056</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.7152194403421308</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-3.338420614375059</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.9307231450079612</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-3.125277021184369</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-4.632313401856569</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.05241019569237607</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.01133558087350155</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.03740424252958528</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.06700898115274979</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-7.895114492129804</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.377636409094931</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-6.593968046262434</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-13.630624243354</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.1195881086281885</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.05272217990513301</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.07793898388252384</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.1823020913218334</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.12741198259135</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.451599430306675</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.2387062647575338</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>4.064111916609368</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.01857765409903935</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.03016635811615424</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.00295349091790263</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.06510750705842344</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
